--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -1,103 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyDebuffResistance" sheetId="1" r:id="rId1"/>
+    <sheet name="EnemyDebuffResistance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>EnemyDebuffResistance</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>110dafa992dea808</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>variant_id</t>
-  </si>
-  <si>
-    <t>category_key</t>
-  </si>
-  <si>
-    <t>value_decimal</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;EnemyVariant.id&gt;</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>length=1..120</t>
-  </si>
-  <si>
-    <t>length=1..32</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -116,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -410,109 +407,261 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>21</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>EnemyDebuffResistance</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>110dafa992dea808</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>category_key</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>value_decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>category_key</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>value_decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;EnemyVariant.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>length=1..120</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length=1..32</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>103</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Burn</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>104</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>105</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>STAT_CTRL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>106</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Burn</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>98</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>98</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>STAT_Confine</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,6 +664,36 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Frozen</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Imprisonment</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,6 +694,51 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>STAT_Confine</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>STAT_Entangle</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,6 +739,51 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>STAT_Confine</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>STAT_Entangle</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,21 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Burn</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,51 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Confine</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Entangle</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,6 +844,36 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Confine</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -874,6 +874,51 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Confine</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Entangle</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,21 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,6 +934,36 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>STAT_Entangle</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,6 +964,21 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,51 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Confine</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Entangle</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,11 +621,11 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>STAT_DOT_Burn</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Frozen</t>
+          <t>STAT_Confine</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -651,16 +651,16 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>STAT_Confine</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frozen</t>
+          <t>Imprisonment</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -681,11 +681,11 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Imprisonment</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Frozen</t>
+          <t>STAT_Confine</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>STAT_Confine</t>
+          <t>STAT_Entangle</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -726,11 +726,11 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>STAT_Entangle</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Frozen</t>
+          <t>STAT_Confine</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>STAT_Confine</t>
+          <t>STAT_Entangle</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -771,31 +771,31 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>STAT_Entangle</t>
+          <t>STAT_DOT_Burn</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>STAT_DOT_Burn</t>
+          <t>STAT_CTRL_Confine</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Confine</t>
+          <t>STAT_CTRL_Entangle</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Entangle</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -831,16 +831,16 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Frozen</t>
+          <t>STAT_CTRL_Confine</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Confine</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -861,16 +861,16 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Frozen</t>
+          <t>STAT_CTRL_Confine</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Confine</t>
+          <t>STAT_CTRL_Entangle</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Entangle</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -906,7 +906,7 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -915,13 +915,13 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Frozen</t>
+          <t>STAT_Entangle</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -951,26 +951,26 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>STAT_Entangle</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Frozen</t>
+          <t>STAT_CTRL_Confine</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Confine</t>
+          <t>STAT_CTRL_Entangle</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Entangle</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1080001</v>
+        <v>1120007</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1021,6 +1021,21 @@
       <c r="D37" t="inlineStr">
         <is>
           <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>106</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Burn</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,6 +1039,21 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Burn</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,6 +1054,21 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Electric</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1069,6 +1069,21 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Poison</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,11 +621,11 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>STAT_DOT_Burn</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Frozen</t>
+          <t>STAT_Confine</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -651,14 +651,434 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Frozen</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Imprisonment</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>STAT_Confine</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>STAT_Entangle</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>STAT_Confine</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>STAT_Entangle</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Burn</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Confine</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Entangle</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Confine</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Confine</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Entangle</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>STAT_Entangle</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Confine</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Entangle</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>106</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Burn</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Burn</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Electric</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Poison</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>1</t>
         </is>

--- a/config/data/EnemyDebuffResistance.xlsx
+++ b/config/data/EnemyDebuffResistance.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyDebuffResistance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyDebuffResistance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,169 +499,182 @@
   </sheetPr>
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="20.7109375" customWidth="1" style="5" min="2" max="2"/>
+    <col width="12.7109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="13.7109375" customWidth="1" style="5" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>EnemyDebuffResistance</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>110dafa992dea808</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>954f91596fbc84e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>variant_id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>category_key</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>value_decimal</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>variant_id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>category_key</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>value_decimal</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;EnemyVariant.id&gt;</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>all</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>length=1..120</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>103</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -590,8 +688,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>104</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -605,8 +705,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>105</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -620,8 +722,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>98</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -635,8 +739,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>98</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -650,8 +756,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>980001</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>980001</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -665,8 +773,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>980001</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>980001</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -680,8 +790,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>990001</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>990001</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -695,8 +807,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>990001</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>990001</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -710,8 +824,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>990001</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>990001</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -725,8 +841,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>1000001</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -740,8 +858,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>1000001</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -755,8 +875,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>1000001</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -770,8 +892,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>1010001</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1010001</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -785,8 +909,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>1020001</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1040001</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -800,8 +926,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>1020001</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1040001</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -815,8 +943,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>1020001</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1040001</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -830,177 +960,199 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>1030001</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1050001</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1060001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1060001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>STAT_Entangle</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1070001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1080001</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>STAT_CTRL_Confine</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1080001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Entangle</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1080001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1120007</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>STAT_CTRL_Frozen</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Burn</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" t="n">
-        <v>1030001</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>STAT_CTRL_Frozen</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1130003</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Burn</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="n">
-        <v>1040001</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>STAT_CTRL_Confine</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="n">
-        <v>1040001</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>STAT_CTRL_Entangle</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="n">
-        <v>1040001</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>STAT_CTRL_Frozen</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>1050001</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>STAT_CTRL_Frozen</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1150002</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>STAT_DOT_Poison</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="n">
-        <v>1060001</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>STAT_CTRL_Frozen</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="n">
-        <v>1060001</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>STAT_Entangle</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="n">
-        <v>1070001</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>STAT_CTRL_Frozen</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="n">
-        <v>1080001</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>STAT_CTRL_Confine</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="n">
-        <v>1080001</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>STAT_CTRL_Entangle</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1080001</v>
+        <v>1020001</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Frozen</t>
+          <t>STAT_CTRL_Confine</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1011,11 +1163,11 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1120007</v>
+        <v>1020001</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>STAT_CTRL_Frozen</t>
+          <t>STAT_CTRL_Entangle</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1026,26 +1178,26 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>106</v>
+        <v>1020001</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>STAT_DOT_Burn</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1130003</v>
+        <v>1140001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>STAT_DOT_Burn</t>
+          <t>STAT_DOT_Electric</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1056,11 +1208,11 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1140001</v>
+        <v>1030001</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STAT_DOT_Electric</t>
+          <t>STAT_CTRL_Confine</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1071,11 +1223,11 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1150002</v>
+        <v>1030001</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>STAT_DOT_Poison</t>
+          <t>STAT_CTRL_Frozen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
